--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF16E5D5-2259-40F9-A4A7-698CD13007F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5E35678-3862-4326-BDC8-FF11F03793BE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BDF853C-1FA9-44F3-A975-A60C867A3CEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{246B6104-EB48-48D0-A766-1CA4610D471A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A80FB33-22D2-47D3-8E20-729262D78B70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8ADBAC64-0D46-47D5-AA01-22B33FB29315}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5E35678-3862-4326-BDC8-FF11F03793BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4BD65FE-23F1-4124-AF0C-16FC855C9322}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{246B6104-EB48-48D0-A766-1CA4610D471A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE9C34D-25D7-4627-8A36-38899DEA22E5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8ADBAC64-0D46-47D5-AA01-22B33FB29315}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52205C13-F0DE-4081-9000-448C736B0740}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4BD65FE-23F1-4124-AF0C-16FC855C9322}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3540A9F9-0193-496F-ADC6-41E6D7E475E1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE9C34D-25D7-4627-8A36-38899DEA22E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9209FDD8-0D98-4A09-BE24-FCB968EA0E20}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52205C13-F0DE-4081-9000-448C736B0740}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1683CEA4-EA34-4BE8-806E-F88C8565886F}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3540A9F9-0193-496F-ADC6-41E6D7E475E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A58D9FF-CDD6-40E8-BC7E-E3177DE18D98}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9209FDD8-0D98-4A09-BE24-FCB968EA0E20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EFE32A9-240F-4667-8B78-13CA4D39C4D3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1683CEA4-EA34-4BE8-806E-F88C8565886F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B008DD0-3384-446E-A46D-054571F50EA2}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A58D9FF-CDD6-40E8-BC7E-E3177DE18D98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1182AB1C-F0F1-47E9-A46B-FF5D453BBC44}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EFE32A9-240F-4667-8B78-13CA4D39C4D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFFE946F-277E-43C4-8365-76998D0D9FAC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B008DD0-3384-446E-A46D-054571F50EA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AA82B8A-05A9-43C2-A02D-EC0BB50E48DF}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1182AB1C-F0F1-47E9-A46B-FF5D453BBC44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD257D08-39D0-4008-84E0-A46897D53622}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFFE946F-277E-43C4-8365-76998D0D9FAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABE4DC1F-9207-40C6-90E1-C842F348C122}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AA82B8A-05A9-43C2-A02D-EC0BB50E48DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73B24167-E1C0-421F-9FD2-A02B75383B45}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD257D08-39D0-4008-84E0-A46897D53622}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94F92B6-CD06-4FE6-9F23-C4BF05E1DF02}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABE4DC1F-9207-40C6-90E1-C842F348C122}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C00EF196-B3BE-4AA2-B2BC-7844453DBAE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73B24167-E1C0-421F-9FD2-A02B75383B45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55ED3CD0-A6E8-4F2B-AE33-8AA1C1722CBD}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94F92B6-CD06-4FE6-9F23-C4BF05E1DF02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4790CB-20F0-4D37-A4F1-348C511F6905}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C00EF196-B3BE-4AA2-B2BC-7844453DBAE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFA1719-0200-45DB-BB9C-D9BC15D2FAD2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55ED3CD0-A6E8-4F2B-AE33-8AA1C1722CBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F18B891-9D02-4586-BBC1-DB2D2FA05152}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4790CB-20F0-4D37-A4F1-348C511F6905}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81EBF857-76E9-4D70-8044-DBAA150E0B99}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFA1719-0200-45DB-BB9C-D9BC15D2FAD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F9D4CFC-2D91-4043-8E4C-8D37CDABCB17}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F18B891-9D02-4586-BBC1-DB2D2FA05152}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FAF6903-E8BD-4194-91E3-AFA7974FB8AD}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81EBF857-76E9-4D70-8044-DBAA150E0B99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E25C8C5-CC47-408D-82DB-E22E558EE892}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F9D4CFC-2D91-4043-8E4C-8D37CDABCB17}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{373A22E8-3B37-4B51-80B9-AA226C2A357E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FAF6903-E8BD-4194-91E3-AFA7974FB8AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{422AF71D-CA0E-448D-8DEA-5D02527431E5}"/>
 </file>
--- a/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
+++ b/Bortoff_Strick_1993/Bortoff_Strick_1993_Table1_snapshot.xlsx
@@ -872,13 +872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E25C8C5-CC47-408D-82DB-E22E558EE892}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BCE8B23-D43E-4EFB-83F2-B7F53E6A7463}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{373A22E8-3B37-4B51-80B9-AA226C2A357E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{741B4450-C174-4A79-AD48-47166C63F340}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{422AF71D-CA0E-448D-8DEA-5D02527431E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68D71E6D-2971-4EFB-8B9E-2F1AF1723998}"/>
 </file>